--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N30_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0003T0006Z000C1N30_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>48.23592122997762</v>
+        <v>7.838337199871364</v>
       </c>
       <c r="D2" t="n">
-        <v>48.29407454704461</v>
+        <v>7.847787113894749</v>
       </c>
       <c r="E2" t="n">
-        <v>6.477270529814986</v>
+        <v>1.052556461094935</v>
       </c>
       <c r="F2" t="n">
-        <v>6.808648470579124</v>
+        <v>1.106405376469107</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>61.78683756597152</v>
+        <v>10.04036110447037</v>
       </c>
       <c r="D3" t="n">
-        <v>62.50485031579513</v>
+        <v>10.15703817631671</v>
       </c>
       <c r="E3" t="n">
-        <v>6.477270529814986</v>
+        <v>1.052556461094935</v>
       </c>
       <c r="F3" t="n">
-        <v>6.808648470579124</v>
+        <v>1.106405376469107</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.16176437344473</v>
+        <v>7.663786710684768</v>
       </c>
       <c r="D4" t="n">
-        <v>47.38515149924493</v>
+        <v>7.700087118627301</v>
       </c>
       <c r="E4" t="n">
-        <v>6.477270529814986</v>
+        <v>1.052556461094935</v>
       </c>
       <c r="F4" t="n">
-        <v>6.808648470579124</v>
+        <v>1.106405376469107</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.33180933770412</v>
+        <v>7.366419017376919</v>
       </c>
       <c r="D5" t="n">
-        <v>45.36011940022651</v>
+        <v>7.371019402536808</v>
       </c>
       <c r="E5" t="n">
-        <v>6.477270529814986</v>
+        <v>1.052556461094935</v>
       </c>
       <c r="F5" t="n">
-        <v>6.808648470579124</v>
+        <v>1.106405376469107</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.60510182529893</v>
+        <v>7.085829046611076</v>
       </c>
       <c r="D6" t="n">
-        <v>43.19828161624565</v>
+        <v>7.019720762639919</v>
       </c>
       <c r="E6" t="n">
-        <v>6.477270529814986</v>
+        <v>1.052556461094935</v>
       </c>
       <c r="F6" t="n">
-        <v>6.808648470579124</v>
+        <v>1.106405376469107</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
